--- a/artfynd/A 13943-2024 artfynd.xlsx
+++ b/artfynd/A 13943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980625</v>
+        <v>117980709</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
+        <v>91772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592572</v>
+        <v>592519</v>
       </c>
       <c r="R2" t="n">
-        <v>6981666</v>
+        <v>6981614</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -785,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980709</v>
+        <v>117980625</v>
       </c>
       <c r="B3" t="n">
-        <v>91772</v>
+        <v>57303</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,38 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592519</v>
+        <v>592572</v>
       </c>
       <c r="R3" t="n">
-        <v>6981614</v>
+        <v>6981666</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>

--- a/artfynd/A 13943-2024 artfynd.xlsx
+++ b/artfynd/A 13943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980709</v>
+        <v>117980625</v>
       </c>
       <c r="B2" t="n">
-        <v>91772</v>
+        <v>57304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592519</v>
+        <v>592572</v>
       </c>
       <c r="R2" t="n">
-        <v>6981614</v>
+        <v>6981666</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980625</v>
+        <v>117980709</v>
       </c>
       <c r="B3" t="n">
-        <v>57303</v>
+        <v>91774</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +797,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592572</v>
+        <v>592519</v>
       </c>
       <c r="R3" t="n">
-        <v>6981666</v>
+        <v>6981614</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
